--- a/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_chi_boss_00001/vd_chi_boss_00001.xlsx
+++ b/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_chi_boss_00001/vd_chi_boss_00001.xlsx
@@ -274,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -342,9 +342,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -680,7 +677,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>ブロック基礎設計_vd_chi_boss_00001</t>
         </is>
@@ -730,19 +727,19 @@
     </row>
     <row r="4" ht="186" customHeight="1">
       <c r="A4" s="6" t="n"/>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>チェンソーマンの世界観を反映したボスブロックです。ボスとして「悪魔が恐れる悪魔 チェンソーマン」（Blue属性・テクニカルロール）が敵ゲート前に降臨します。プレイヤーはボスを倒すまで敵ゲートへのダメージが無効であるため、ボスの撃破が最優先課題となります。ボス登場から0.5秒後にゾンビが3体出現してプレッシャーを与え、さらに3秒後にファントムが3体追加出現することで継続的な圧力を維持します。チェンソーマンはBlue属性・テクニカルロールで高い移動速度（spd=50）と高コンボ（combo=5）を持つ強敵であり、「悪魔が恐れる悪魔」の名に恥じない圧倒的な存在感を演出します。フロア係数 1.00 を基準とした設計で、1ダメージ受けるとすぐに進軍を開始する仕様により、緊張感のある戦闘体験を提供します。</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n"/>
-      <c r="D4" s="28" t="n"/>
-      <c r="E4" s="28" t="n"/>
-      <c r="F4" s="28" t="n"/>
-      <c r="G4" s="28" t="n"/>
-      <c r="H4" s="28" t="n"/>
-      <c r="I4" s="28" t="n"/>
-      <c r="J4" s="29" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="28" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="n"/>
@@ -845,35 +842,35 @@
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>1行</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>なし（デフォルトグループのみ）</t>
         </is>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>3行</t>
         </is>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="26" t="n">
         <v>202604010</v>
       </c>
       <c r="I9" s="2" t="n"/>
@@ -972,25 +969,29 @@
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>行1</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>1コマ</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr"/>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>glo_00016</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -1216,36 +1217,36 @@
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>c_chi_00002_vd_Boss_Blue</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>悪魔が恐れる悪魔 チェンソーマン</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Blue（青属性）</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="29" t="n">
         <v>400000</v>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="26" t="n">
         <v>450</v>
       </c>
-      <c r="H26" s="27" t="n">
+      <c r="H26" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="I26" s="26" t="inlineStr">
         <is>
           <t>ボス（c_キャラ）</t>
         </is>
@@ -1257,38 +1258,38 @@
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>e_chi_00101_vd_Normal_Blue</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>ゾンビ</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>Blue（青属性）</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="26" t="n">
         <v>320</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="26" t="n">
         <v>35</v>
       </c>
-      <c r="I27" s="27" t="inlineStr">
-        <is>
-          <t>雑魚</t>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（e_キャラ）</t>
         </is>
       </c>
       <c r="J27" s="2" t="n"/>
@@ -1298,36 +1299,36 @@
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>ファントム</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Colorless（無属性）</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="26" t="n">
         <v>34</v>
       </c>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>雑魚（共通）</t>
         </is>
@@ -1536,33 +1537,33 @@
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="27" t="n">
+      <c r="B40" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>InitialSummon</t>
         </is>
       </c>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>c_chi_00002_vd_Boss_Blue</t>
         </is>
       </c>
-      <c r="F40" s="27" t="inlineStr">
+      <c r="F40" s="26" t="inlineStr">
         <is>
           <t>悪魔が恐れる悪魔 チェンソーマン</t>
         </is>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="27" t="inlineStr">
-        <is>
-          <t>ボス降臨・summon_position=1.7（ゲート付近）</t>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>開幕ボス・summon_position=1.7・Bossオーラ・Damage 1で進軍</t>
         </is>
       </c>
       <c r="I40" s="2" t="n"/>
@@ -1573,33 +1574,33 @@
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="27" t="n">
+      <c r="B41" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="D41" s="27" t="n">
+      <c r="D41" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="E41" s="27" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>e_chi_00101_vd_Normal_Blue</t>
         </is>
       </c>
-      <c r="F41" s="27" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>ゾンビ</t>
         </is>
       </c>
-      <c r="G41" s="27" t="n">
+      <c r="G41" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="27" t="inlineStr">
-        <is>
-          <t>0.5秒後に3体出現・プレッシャー付与</t>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>3体追加・Blue属性防御型</t>
         </is>
       </c>
       <c r="I41" s="2" t="n"/>
@@ -1610,33 +1611,33 @@
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="27" t="n">
+      <c r="B42" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="27" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="D42" s="30" t="n">
+      <c r="D42" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="E42" s="27" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="F42" s="27" t="inlineStr">
+      <c r="F42" s="26" t="inlineStr">
         <is>
           <t>ファントム</t>
         </is>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="G42" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="27" t="inlineStr">
-        <is>
-          <t>3秒後に3体追加・継続的な圧力</t>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>3体追加・合計7体</t>
         </is>
       </c>
       <c r="I42" s="2" t="n"/>
@@ -1871,10 +1872,10 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="D57" s="28" t="n"/>
-      <c r="E57" s="28" t="n"/>
-      <c r="F57" s="28" t="n"/>
-      <c r="G57" s="29" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="28" t="n"/>
       <c r="H57" s="16" t="n"/>
       <c r="I57" s="16" t="n"/>
       <c r="J57" s="16" t="n"/>
@@ -1890,10 +1891,10 @@
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr"/>
-      <c r="D58" s="28" t="n"/>
-      <c r="E58" s="28" t="n"/>
-      <c r="F58" s="28" t="n"/>
-      <c r="G58" s="29" t="n"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="28" t="n"/>
       <c r="H58" s="16" t="n"/>
       <c r="I58" s="16" t="n"/>
       <c r="J58" s="16" t="n"/>
@@ -1909,10 +1910,10 @@
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr"/>
-      <c r="D59" s="28" t="n"/>
-      <c r="E59" s="28" t="n"/>
-      <c r="F59" s="28" t="n"/>
-      <c r="G59" s="29" t="n"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="28" t="n"/>
       <c r="H59" s="16" t="n"/>
       <c r="I59" s="16" t="n"/>
       <c r="J59" s="16" t="n"/>
@@ -2022,468 +2023,548 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ENABLE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>sequence_set_id</t>
         </is>
       </c>
-      <c r="D1" s="31" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>sequence_group_id</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>sequence_element_id</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>priority_sequence_element_id</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>condition_type</t>
         </is>
       </c>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>condition_value</t>
         </is>
       </c>
-      <c r="I1" s="31" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>action_type</t>
         </is>
       </c>
-      <c r="J1" s="31" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>action_value</t>
         </is>
       </c>
-      <c r="K1" s="31" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>action_value2</t>
         </is>
       </c>
-      <c r="L1" s="31" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>summon_count</t>
         </is>
       </c>
-      <c r="M1" s="31" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>summon_interval</t>
         </is>
       </c>
-      <c r="N1" s="31" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>summon_animation_type</t>
         </is>
       </c>
-      <c r="O1" s="31" t="inlineStr">
+      <c r="O1" s="30" t="inlineStr">
         <is>
           <t>summon_position</t>
         </is>
       </c>
-      <c r="P1" s="31" t="inlineStr">
+      <c r="P1" s="30" t="inlineStr">
         <is>
           <t>move_start_condition_type</t>
         </is>
       </c>
-      <c r="Q1" s="31" t="inlineStr">
+      <c r="Q1" s="30" t="inlineStr">
         <is>
           <t>move_start_condition_value</t>
         </is>
       </c>
-      <c r="R1" s="31" t="inlineStr">
+      <c r="R1" s="30" t="inlineStr">
         <is>
           <t>move_stop_condition_type</t>
         </is>
       </c>
-      <c r="S1" s="31" t="inlineStr">
+      <c r="S1" s="30" t="inlineStr">
         <is>
           <t>move_stop_condition_value</t>
         </is>
       </c>
-      <c r="T1" s="31" t="inlineStr">
+      <c r="T1" s="30" t="inlineStr">
         <is>
           <t>move_restart_condition_type</t>
         </is>
       </c>
-      <c r="U1" s="31" t="inlineStr">
+      <c r="U1" s="30" t="inlineStr">
         <is>
           <t>move_restart_condition_value</t>
         </is>
       </c>
-      <c r="V1" s="31" t="inlineStr">
+      <c r="V1" s="30" t="inlineStr">
         <is>
           <t>move_loop_count</t>
         </is>
       </c>
-      <c r="W1" s="31" t="inlineStr">
+      <c r="W1" s="30" t="inlineStr">
         <is>
           <t>is_summon_unit_outpost_damage_invalidation</t>
         </is>
       </c>
-      <c r="X1" s="31" t="inlineStr">
+      <c r="X1" s="30" t="inlineStr">
         <is>
           <t>last_boss_trigger</t>
         </is>
       </c>
-      <c r="Y1" s="31" t="inlineStr">
+      <c r="Y1" s="30" t="inlineStr">
         <is>
           <t>aura_type</t>
         </is>
       </c>
-      <c r="Z1" s="31" t="inlineStr">
+      <c r="Z1" s="30" t="inlineStr">
         <is>
           <t>death_type</t>
         </is>
       </c>
-      <c r="AA1" s="31" t="inlineStr">
+      <c r="AA1" s="30" t="inlineStr">
         <is>
           <t>enemy_hp_coef</t>
         </is>
       </c>
-      <c r="AB1" s="31" t="inlineStr">
+      <c r="AB1" s="30" t="inlineStr">
         <is>
           <t>enemy_attack_coef</t>
         </is>
       </c>
-      <c r="AC1" s="31" t="inlineStr">
+      <c r="AC1" s="30" t="inlineStr">
         <is>
           <t>enemy_speed_coef</t>
         </is>
       </c>
-      <c r="AD1" s="31" t="inlineStr">
+      <c r="AD1" s="30" t="inlineStr">
         <is>
           <t>override_drop_battle_point</t>
         </is>
       </c>
-      <c r="AE1" s="31" t="inlineStr">
+      <c r="AE1" s="30" t="inlineStr">
         <is>
           <t>defeated_score</t>
         </is>
       </c>
-      <c r="AF1" s="31" t="inlineStr">
+      <c r="AF1" s="30" t="inlineStr">
         <is>
           <t>action_delay</t>
         </is>
       </c>
-      <c r="AG1" s="31" t="inlineStr">
+      <c r="AG1" s="30" t="inlineStr">
         <is>
           <t>deactivation_condition_type</t>
         </is>
       </c>
-      <c r="AH1" s="31" t="inlineStr">
+      <c r="AH1" s="30" t="inlineStr">
         <is>
           <t>deactivation_condition_value</t>
         </is>
       </c>
-      <c r="AI1" s="31" t="inlineStr">
+      <c r="AI1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001_1</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr"/>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr"/>
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr"/>
-      <c r="G2" s="32" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>InitialSummon</t>
         </is>
       </c>
-      <c r="H2" s="32" t="inlineStr">
+      <c r="H2" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr">
+      <c r="I2" s="31" t="inlineStr">
         <is>
           <t>SummonEnemy</t>
         </is>
       </c>
-      <c r="J2" s="32" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>c_chi_00002_vd_Boss_Blue</t>
         </is>
       </c>
-      <c r="K2" s="32" t="inlineStr"/>
-      <c r="L2" s="32" t="inlineStr">
+      <c r="K2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M2" s="32" t="inlineStr"/>
-      <c r="N2" s="32" t="inlineStr"/>
-      <c r="O2" s="32" t="inlineStr">
+      <c r="M2" s="31" t="inlineStr"/>
+      <c r="N2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="P2" s="32" t="inlineStr">
+      <c r="P2" s="31" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="32" t="inlineStr">
+      <c r="Q2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" s="32" t="inlineStr"/>
-      <c r="S2" s="32" t="inlineStr"/>
-      <c r="T2" s="32" t="inlineStr"/>
-      <c r="U2" s="32" t="inlineStr"/>
-      <c r="V2" s="32" t="inlineStr"/>
-      <c r="W2" s="32" t="inlineStr"/>
-      <c r="X2" s="32" t="inlineStr"/>
-      <c r="Y2" s="32" t="inlineStr">
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S2" s="31" t="inlineStr"/>
+      <c r="T2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr"/>
+      <c r="W2" s="31" t="inlineStr"/>
+      <c r="X2" s="31" t="inlineStr"/>
+      <c r="Y2" s="31" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="Z2" s="32" t="inlineStr"/>
-      <c r="AA2" s="32" t="inlineStr">
+      <c r="Z2" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="32" t="inlineStr">
+      <c r="AB2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" s="32" t="inlineStr">
+      <c r="AC2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD2" s="32" t="inlineStr"/>
-      <c r="AE2" s="32" t="inlineStr"/>
-      <c r="AF2" s="32" t="inlineStr"/>
-      <c r="AG2" s="32" t="inlineStr"/>
-      <c r="AH2" s="32" t="inlineStr"/>
-      <c r="AI2" s="32" t="inlineStr">
+      <c r="AD2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr"/>
+      <c r="AG2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH2" s="31" t="inlineStr"/>
+      <c r="AI2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001_2</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr"/>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr"/>
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr"/>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="F3" s="31" t="inlineStr"/>
+      <c r="G3" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="31" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
+      <c r="I3" s="31" t="inlineStr">
         <is>
           <t>SummonEnemy</t>
         </is>
       </c>
-      <c r="J3" s="32" t="inlineStr">
+      <c r="J3" s="31" t="inlineStr">
         <is>
           <t>e_chi_00101_vd_Normal_Blue</t>
         </is>
       </c>
-      <c r="K3" s="32" t="inlineStr"/>
-      <c r="L3" s="32" t="inlineStr">
+      <c r="K3" s="31" t="inlineStr"/>
+      <c r="L3" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M3" s="32" t="inlineStr"/>
-      <c r="N3" s="32" t="inlineStr"/>
-      <c r="O3" s="32" t="inlineStr"/>
-      <c r="P3" s="32" t="inlineStr"/>
-      <c r="Q3" s="32" t="inlineStr"/>
-      <c r="R3" s="32" t="inlineStr"/>
-      <c r="S3" s="32" t="inlineStr"/>
-      <c r="T3" s="32" t="inlineStr"/>
-      <c r="U3" s="32" t="inlineStr"/>
-      <c r="V3" s="32" t="inlineStr"/>
-      <c r="W3" s="32" t="inlineStr"/>
-      <c r="X3" s="32" t="inlineStr"/>
-      <c r="Y3" s="32" t="inlineStr">
+      <c r="M3" s="31" t="inlineStr"/>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="inlineStr"/>
+      <c r="P3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q3" s="31" t="inlineStr"/>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S3" s="31" t="inlineStr"/>
+      <c r="T3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U3" s="31" t="inlineStr"/>
+      <c r="V3" s="31" t="inlineStr"/>
+      <c r="W3" s="31" t="inlineStr"/>
+      <c r="X3" s="31" t="inlineStr"/>
+      <c r="Y3" s="31" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="Z3" s="32" t="inlineStr"/>
-      <c r="AA3" s="32" t="inlineStr">
+      <c r="Z3" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA3" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="32" t="inlineStr">
+      <c r="AB3" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" s="32" t="inlineStr">
+      <c r="AC3" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD3" s="32" t="inlineStr"/>
-      <c r="AE3" s="32" t="inlineStr"/>
-      <c r="AF3" s="32" t="inlineStr"/>
-      <c r="AG3" s="32" t="inlineStr"/>
-      <c r="AH3" s="32" t="inlineStr"/>
-      <c r="AI3" s="32" t="inlineStr">
+      <c r="AD3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr"/>
+      <c r="AG3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH3" s="31" t="inlineStr"/>
+      <c r="AI3" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001_3</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr"/>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr"/>
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr"/>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>SummonEnemy</t>
         </is>
       </c>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr"/>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr"/>
+      <c r="L4" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr"/>
-      <c r="N4" s="32" t="inlineStr"/>
-      <c r="O4" s="32" t="inlineStr"/>
-      <c r="P4" s="32" t="inlineStr"/>
-      <c r="Q4" s="32" t="inlineStr"/>
-      <c r="R4" s="32" t="inlineStr"/>
-      <c r="S4" s="32" t="inlineStr"/>
-      <c r="T4" s="32" t="inlineStr"/>
-      <c r="U4" s="32" t="inlineStr"/>
-      <c r="V4" s="32" t="inlineStr"/>
-      <c r="W4" s="32" t="inlineStr"/>
-      <c r="X4" s="32" t="inlineStr"/>
-      <c r="Y4" s="32" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr"/>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr"/>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr"/>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr"/>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U4" s="31" t="inlineStr"/>
+      <c r="V4" s="31" t="inlineStr"/>
+      <c r="W4" s="31" t="inlineStr"/>
+      <c r="X4" s="31" t="inlineStr"/>
+      <c r="Y4" s="31" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="Z4" s="32" t="inlineStr"/>
-      <c r="AA4" s="32" t="inlineStr">
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="32" t="inlineStr">
+      <c r="AB4" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" s="32" t="inlineStr">
+      <c r="AC4" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD4" s="32" t="inlineStr"/>
-      <c r="AE4" s="32" t="inlineStr"/>
-      <c r="AF4" s="32" t="inlineStr"/>
-      <c r="AG4" s="32" t="inlineStr"/>
-      <c r="AH4" s="32" t="inlineStr"/>
-      <c r="AI4" s="32" t="inlineStr">
+      <c r="AD4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr"/>
+      <c r="AG4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH4" s="31" t="inlineStr"/>
+      <c r="AI4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -2504,62 +2585,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ENABLE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="D1" s="31" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>is_damage_invalidation</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>outpost_asset_key</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>artwork_asset_key</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr"/>
-      <c r="E2" s="32" t="inlineStr"/>
-      <c r="F2" s="32" t="inlineStr"/>
-      <c r="G2" s="32" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr"/>
+      <c r="E2" s="31" t="inlineStr"/>
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -2580,204 +2661,204 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ENABLE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>mst_auto_player_sequence_id</t>
         </is>
       </c>
-      <c r="D1" s="31" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>mst_auto_player_sequence_set_id</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>bgm_asset_key</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>boss_bgm_asset_key</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>loop_background_asset_key</t>
         </is>
       </c>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>player_outpost_asset_key</t>
         </is>
       </c>
-      <c r="I1" s="31" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>mst_page_id</t>
         </is>
       </c>
-      <c r="J1" s="31" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>mst_enemy_outpost_id</t>
         </is>
       </c>
-      <c r="K1" s="31" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>mst_defense_target_id</t>
         </is>
       </c>
-      <c r="L1" s="31" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>boss_mst_enemy_stage_parameter_id</t>
         </is>
       </c>
-      <c r="M1" s="31" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>boss_count</t>
         </is>
       </c>
-      <c r="N1" s="31" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>normal_enemy_hp_coef</t>
         </is>
       </c>
-      <c r="O1" s="31" t="inlineStr">
+      <c r="O1" s="30" t="inlineStr">
         <is>
           <t>normal_enemy_attack_coef</t>
         </is>
       </c>
-      <c r="P1" s="31" t="inlineStr">
+      <c r="P1" s="30" t="inlineStr">
         <is>
           <t>normal_enemy_speed_coef</t>
         </is>
       </c>
-      <c r="Q1" s="31" t="inlineStr">
+      <c r="Q1" s="30" t="inlineStr">
         <is>
           <t>boss_enemy_hp_coef</t>
         </is>
       </c>
-      <c r="R1" s="31" t="inlineStr">
+      <c r="R1" s="30" t="inlineStr">
         <is>
           <t>boss_enemy_attack_coef</t>
         </is>
       </c>
-      <c r="S1" s="31" t="inlineStr">
+      <c r="S1" s="30" t="inlineStr">
         <is>
           <t>boss_enemy_speed_coef</t>
         </is>
       </c>
-      <c r="T1" s="31" t="inlineStr">
+      <c r="T1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
       </c>
-      <c r="U1" s="31" t="inlineStr">
+      <c r="U1" s="30" t="inlineStr">
         <is>
           <t>result_tips.ja</t>
         </is>
       </c>
-      <c r="V1" s="31" t="inlineStr">
+      <c r="V1" s="30" t="inlineStr">
         <is>
           <t>description.ja</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>SSE_SBG_003_004</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr"/>
-      <c r="G2" s="32" t="inlineStr"/>
-      <c r="H2" s="32" t="inlineStr"/>
-      <c r="I2" s="32" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr"/>
+      <c r="H2" s="31" t="inlineStr"/>
+      <c r="I2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="J2" s="32" t="inlineStr">
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="K2" s="32" t="inlineStr"/>
-      <c r="L2" s="32" t="inlineStr">
+      <c r="K2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr">
         <is>
           <t>c_chi_00002_vd_Boss_Blue</t>
         </is>
       </c>
-      <c r="M2" s="32" t="inlineStr">
+      <c r="M2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" s="32" t="inlineStr">
+      <c r="N2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" s="32" t="inlineStr">
+      <c r="O2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" s="32" t="inlineStr">
+      <c r="P2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" s="32" t="inlineStr">
+      <c r="Q2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" s="32" t="inlineStr">
+      <c r="R2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S2" s="32" t="inlineStr">
+      <c r="S2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T2" s="32" t="inlineStr">
+      <c r="T2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
       </c>
-      <c r="U2" s="32" t="inlineStr"/>
-      <c r="V2" s="32" t="inlineStr"/>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2794,298 +2875,306 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ENABLE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>mst_page_id</t>
         </is>
       </c>
-      <c r="D1" s="31" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>height</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>koma_line_layout_asset_key</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>koma1_asset_key</t>
         </is>
       </c>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>koma1_width</t>
         </is>
       </c>
-      <c r="I1" s="31" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>koma1_back_ground_offset</t>
         </is>
       </c>
-      <c r="J1" s="31" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>koma1_effect_type</t>
         </is>
       </c>
-      <c r="K1" s="31" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>koma1_effect_parameter1</t>
         </is>
       </c>
-      <c r="L1" s="31" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>koma1_effect_parameter2</t>
         </is>
       </c>
-      <c r="M1" s="31" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>koma1_effect_target_side</t>
         </is>
       </c>
-      <c r="N1" s="31" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>koma1_effect_target_colors</t>
         </is>
       </c>
-      <c r="O1" s="31" t="inlineStr">
+      <c r="O1" s="30" t="inlineStr">
         <is>
           <t>koma1_effect_target_roles</t>
         </is>
       </c>
-      <c r="P1" s="31" t="inlineStr">
+      <c r="P1" s="30" t="inlineStr">
         <is>
           <t>koma2_asset_key</t>
         </is>
       </c>
-      <c r="Q1" s="31" t="inlineStr">
+      <c r="Q1" s="30" t="inlineStr">
         <is>
           <t>koma2_width</t>
         </is>
       </c>
-      <c r="R1" s="31" t="inlineStr">
+      <c r="R1" s="30" t="inlineStr">
         <is>
           <t>koma2_back_ground_offset</t>
         </is>
       </c>
-      <c r="S1" s="31" t="inlineStr">
+      <c r="S1" s="30" t="inlineStr">
         <is>
           <t>koma2_effect_type</t>
         </is>
       </c>
-      <c r="T1" s="31" t="inlineStr">
+      <c r="T1" s="30" t="inlineStr">
         <is>
           <t>koma2_effect_parameter1</t>
         </is>
       </c>
-      <c r="U1" s="31" t="inlineStr">
+      <c r="U1" s="30" t="inlineStr">
         <is>
           <t>koma2_effect_parameter2</t>
         </is>
       </c>
-      <c r="V1" s="31" t="inlineStr">
+      <c r="V1" s="30" t="inlineStr">
         <is>
           <t>koma2_effect_target_side</t>
         </is>
       </c>
-      <c r="W1" s="31" t="inlineStr">
+      <c r="W1" s="30" t="inlineStr">
         <is>
           <t>koma2_effect_target_colors</t>
         </is>
       </c>
-      <c r="X1" s="31" t="inlineStr">
+      <c r="X1" s="30" t="inlineStr">
         <is>
           <t>koma2_effect_target_roles</t>
         </is>
       </c>
-      <c r="Y1" s="31" t="inlineStr">
+      <c r="Y1" s="30" t="inlineStr">
         <is>
           <t>koma3_asset_key</t>
         </is>
       </c>
-      <c r="Z1" s="31" t="inlineStr">
+      <c r="Z1" s="30" t="inlineStr">
         <is>
           <t>koma3_width</t>
         </is>
       </c>
-      <c r="AA1" s="31" t="inlineStr">
+      <c r="AA1" s="30" t="inlineStr">
         <is>
           <t>koma3_back_ground_offset</t>
         </is>
       </c>
-      <c r="AB1" s="31" t="inlineStr">
+      <c r="AB1" s="30" t="inlineStr">
         <is>
           <t>koma3_effect_type</t>
         </is>
       </c>
-      <c r="AC1" s="31" t="inlineStr">
+      <c r="AC1" s="30" t="inlineStr">
         <is>
           <t>koma3_effect_parameter1</t>
         </is>
       </c>
-      <c r="AD1" s="31" t="inlineStr">
+      <c r="AD1" s="30" t="inlineStr">
         <is>
           <t>koma3_effect_parameter2</t>
         </is>
       </c>
-      <c r="AE1" s="31" t="inlineStr">
+      <c r="AE1" s="30" t="inlineStr">
         <is>
           <t>koma3_effect_target_side</t>
         </is>
       </c>
-      <c r="AF1" s="31" t="inlineStr">
+      <c r="AF1" s="30" t="inlineStr">
         <is>
           <t>koma3_effect_target_colors</t>
         </is>
       </c>
-      <c r="AG1" s="31" t="inlineStr">
+      <c r="AG1" s="30" t="inlineStr">
         <is>
           <t>koma3_effect_target_roles</t>
         </is>
       </c>
-      <c r="AH1" s="31" t="inlineStr">
+      <c r="AH1" s="30" t="inlineStr">
         <is>
           <t>koma4_asset_key</t>
         </is>
       </c>
-      <c r="AI1" s="31" t="inlineStr">
+      <c r="AI1" s="30" t="inlineStr">
         <is>
           <t>koma4_width</t>
         </is>
       </c>
-      <c r="AJ1" s="31" t="inlineStr">
+      <c r="AJ1" s="30" t="inlineStr">
         <is>
           <t>koma4_back_ground_offset</t>
         </is>
       </c>
-      <c r="AK1" s="31" t="inlineStr">
+      <c r="AK1" s="30" t="inlineStr">
         <is>
           <t>koma4_effect_type</t>
         </is>
       </c>
-      <c r="AL1" s="31" t="inlineStr">
+      <c r="AL1" s="30" t="inlineStr">
         <is>
           <t>koma4_effect_parameter1</t>
         </is>
       </c>
-      <c r="AM1" s="31" t="inlineStr">
+      <c r="AM1" s="30" t="inlineStr">
         <is>
           <t>koma4_effect_parameter2</t>
         </is>
       </c>
-      <c r="AN1" s="31" t="inlineStr">
+      <c r="AN1" s="30" t="inlineStr">
         <is>
           <t>koma4_effect_target_side</t>
         </is>
       </c>
-      <c r="AO1" s="31" t="inlineStr">
+      <c r="AO1" s="30" t="inlineStr">
         <is>
           <t>koma4_effect_target_colors</t>
         </is>
       </c>
-      <c r="AP1" s="31" t="inlineStr">
+      <c r="AP1" s="30" t="inlineStr">
         <is>
           <t>koma4_effect_target_roles</t>
         </is>
       </c>
-      <c r="AQ1" s="31" t="inlineStr">
+      <c r="AQ1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001_1</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr"/>
-      <c r="G2" s="32" t="inlineStr"/>
-      <c r="H2" s="32" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>glo_00016</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr"/>
-      <c r="J2" s="32" t="inlineStr">
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K2" s="32" t="inlineStr"/>
-      <c r="L2" s="32" t="inlineStr"/>
-      <c r="M2" s="32" t="inlineStr">
+      <c r="K2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr"/>
+      <c r="M2" s="31" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="N2" s="32" t="inlineStr"/>
-      <c r="O2" s="32" t="inlineStr"/>
-      <c r="P2" s="32" t="inlineStr"/>
-      <c r="Q2" s="32" t="inlineStr"/>
-      <c r="R2" s="32" t="inlineStr"/>
-      <c r="S2" s="32" t="inlineStr"/>
-      <c r="T2" s="32" t="inlineStr"/>
-      <c r="U2" s="32" t="inlineStr"/>
-      <c r="V2" s="32" t="inlineStr"/>
-      <c r="W2" s="32" t="inlineStr"/>
-      <c r="X2" s="32" t="inlineStr"/>
-      <c r="Y2" s="32" t="inlineStr"/>
-      <c r="Z2" s="32" t="inlineStr"/>
-      <c r="AA2" s="32" t="inlineStr"/>
-      <c r="AB2" s="32" t="inlineStr"/>
-      <c r="AC2" s="32" t="inlineStr"/>
-      <c r="AD2" s="32" t="inlineStr"/>
-      <c r="AE2" s="32" t="inlineStr"/>
-      <c r="AF2" s="32" t="inlineStr"/>
-      <c r="AG2" s="32" t="inlineStr"/>
-      <c r="AH2" s="32" t="inlineStr"/>
-      <c r="AI2" s="32" t="inlineStr"/>
-      <c r="AJ2" s="32" t="inlineStr"/>
-      <c r="AK2" s="32" t="inlineStr"/>
-      <c r="AL2" s="32" t="inlineStr"/>
-      <c r="AM2" s="32" t="inlineStr"/>
-      <c r="AN2" s="32" t="inlineStr"/>
-      <c r="AO2" s="32" t="inlineStr"/>
-      <c r="AP2" s="32" t="inlineStr"/>
-      <c r="AQ2" s="32" t="inlineStr">
+      <c r="N2" s="31" t="inlineStr"/>
+      <c r="O2" s="31" t="inlineStr"/>
+      <c r="P2" s="31" t="inlineStr"/>
+      <c r="Q2" s="31" t="inlineStr"/>
+      <c r="R2" s="31" t="inlineStr"/>
+      <c r="S2" s="31" t="inlineStr"/>
+      <c r="T2" s="31" t="inlineStr"/>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr"/>
+      <c r="W2" s="31" t="inlineStr"/>
+      <c r="X2" s="31" t="inlineStr"/>
+      <c r="Y2" s="31" t="inlineStr"/>
+      <c r="Z2" s="31" t="inlineStr"/>
+      <c r="AA2" s="31" t="inlineStr"/>
+      <c r="AB2" s="31" t="inlineStr"/>
+      <c r="AC2" s="31" t="inlineStr"/>
+      <c r="AD2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr"/>
+      <c r="AF2" s="31" t="inlineStr"/>
+      <c r="AG2" s="31" t="inlineStr"/>
+      <c r="AH2" s="31" t="inlineStr"/>
+      <c r="AI2" s="31" t="inlineStr"/>
+      <c r="AJ2" s="31" t="inlineStr"/>
+      <c r="AK2" s="31" t="inlineStr"/>
+      <c r="AL2" s="31" t="inlineStr"/>
+      <c r="AM2" s="31" t="inlineStr"/>
+      <c r="AN2" s="31" t="inlineStr"/>
+      <c r="AO2" s="31" t="inlineStr"/>
+      <c r="AP2" s="31" t="inlineStr"/>
+      <c r="AQ2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3106,34 +3195,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ENABLE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>vd_chi_boss_00001</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
